--- a/radar-unseen/sources.xlsx
+++ b/radar-unseen/sources.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Flux riche (100 articles)</t>
@@ -519,8 +518,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,8 +540,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,7 +562,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Flux riche (100 articles)</t>
@@ -595,7 +589,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Flux riche (100 articles)</t>
@@ -623,8 +616,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -647,8 +638,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -671,7 +660,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Flux pauvre (2 articles au test)</t>
@@ -699,7 +687,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Flux riche (100 articles)</t>
@@ -727,8 +714,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -751,8 +736,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -775,7 +758,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Journal généraliste : beaucoup de bruit, filtrage strict</t>
@@ -808,7 +790,6 @@
           <t>Concurrent</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -831,8 +812,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -860,7 +839,6 @@
           <t>Tendance clientele</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -883,7 +861,6 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Pas de catégorie imposée : l'alerte ramène beaucoup de potins sur les artistes. Le tri se fait par les mots-clés de salles dans l'onglet Themes</t>
@@ -916,7 +893,6 @@
           <t>Ouverture</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -944,7 +920,6 @@
           <t>Nomination</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -972,7 +947,6 @@
           <t>Nomination</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -980,7 +954,6 @@
           <t>Alerte Google - Presse hotellerie FR (a creer)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Google Alerte</t>
@@ -991,7 +964,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Coller ici le lien RSS une fois l'alerte créée, puis mettre Actif = oui</t>
@@ -1004,7 +976,6 @@
           <t>Alerte Google - Luxe et voyage international (a creer)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Google Alerte</t>
@@ -1015,7 +986,6 @@
           <t>non</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Coller ici le lien RSS une fois l'alerte créée, puis mettre Actif = oui</t>
@@ -1028,7 +998,6 @@
           <t>Alerte Google - Aviation, yachting et Maurice (a creer)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>Google Alerte</t>
@@ -1039,10 +1008,201 @@
           <t>non</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>Coller ici le lien RSS une fois l'alerte créée, puis mettre Actif = oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Alerte Google - Tour-operateurs Chine-Asie vers Paris (a creer)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.google.com/alerts/feeds/04631949256830863565/3860368697969530428</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Google Alerte</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Tour-operateur</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Recherche suggérée : (tour operator OR agence de voyage OR DMC OR voyagiste) (Paris OR France) (partenariat OR "nouveau programme" OR bureau). Coller ici le lien RSS une fois l'alerte créée, puis mettre Actif = oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Alerte Google - Tourisme chinois France, tendance (a creer)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.google.com/alerts/feeds/04631949256830863565/2588257271187485020</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Google Alerte</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tour-operateur</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Recherche suggérée : tourisme chinois (Paris OR France) (croissance OR reprise OR vols OR visa). Coller ici le lien RSS une fois l'alerte créée, puis mettre Actif = oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Alerte Google - Agences Moyen-Orient vers Paris (a creer)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.google.com/alerts/feeds/04631949256830863565/8893673814457499888</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Google Alerte</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Tour-operateur</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Recherche suggérée : (tour operator OR agence de voyage OR DMC) (Dubai OR "Abu Dhabi" OR Riyadh OR Qatar OR Golfe) (Paris OR France) (partenariat OR programme). Coller ici le lien RSS une fois l'alerte créée, puis mettre Actif = oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Alerte Google - Guides shopping Paris (a creer)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/alerts/feeds/04631949256830863565/7894814852791298239</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Google Alerte</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Tour-operateur</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Recherche suggérée : (guide OR "personal shopping" OR "shopping tour") Paris ("Galeries Lafayette" OR luxe OR "duty free" OR detaxe). Coller ici le lien RSS une fois l'alerte créée, puis mettre Actif = oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Alerte Google - Vols et visas Chine-Golfe vers France (a creer)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/alerts/feeds/04631949256830863565/17733186340971705382</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Google Alerte</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Tour-operateur</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Recherche suggérée : ("vol direct" OR "direct flight" OR visa) (Chine OR China OR Golfe OR Gulf) France (Paris OR touristes OR voyageurs). Coller ici le lien RSS une fois l'alerte créée, puis mettre Actif = oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Alerte Google - Tour-operateurs Inde vers Paris (a creer)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/alerts/feeds/04631949256830863565/17535519683538808538</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Google Alerte</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Tour-operateur</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Recherche suggérée : (tour operator OR agence de voyage OR DMC) India (Paris OR France) (partenariat OR "nouveau programme" OR bureau). Coller ici le lien RSS une fois l'alerte créée, puis mettre Actif = oui</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1297,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Si tu remplis (Nomination, Ouverture, Evenement, Tendance clientele, Concurrent), tous les articles</t>
@@ -1145,7 +1304,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>de cette source reçoivent cette catégorie et sont gardés même si aucun mot-clé ne correspond.</t>
@@ -1153,7 +1311,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Utile pour tes Google Alertes, qui ont déjà fait le tri en amont.</t>
@@ -1171,10 +1328,6 @@
           <t>Tes remarques personnelles. Le script ne les lit pas.</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
